--- a/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près. Papa dit : tu restes avec moi. Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+          <t>Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près. Tu restes avec moi. Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près.
+papa|Tu restes avec moi.
+narrateur|Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille est à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille reste avec papa. L'accompagnant est là. La main est tenue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Domitille et papa rentrent avec l'album. Ils marchent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Domitille est à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Domitille reste avec papa. L'accompagnant est là. La main est tenue.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Domitille et papa rentrent avec l'album. Ils marchent ensemble.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Domitille reste avec papa</t>
+          <t>Le signet dans le gros livre</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un signet dépasse. Le tapis cache les pas. Victorina choisit un album bleu. Elle reste avec l'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près. Tu restes avec moi. Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
+          <t>Un signet dépasse d'un gros livre. Il est rouge, tout mince. Le tapis cache les pas. On n'entend presque plus les chaussures. Un rayon de soleil glisse entre les rayons. La poussière y danse, tout doux. Ça sent le papier et le bois. Victorina vit ici, avec papa. Papa, le signet dépasse ! Oui. Il garde la page. Tu vois le rayon de soleil ? Oui. Il est tout jaune. En ce moment, ils marchent entre les livres. Papa tient la main de Victorina. La main est chaude. Les pieds de Victorina restent près. Papa est l'accompagnant. Victorina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils voient des livres colorés. Un album a une couverture bleue. Un bateau blanc est dessus. Le bateau ! On le regarde ensemble. Papa prend l'album. Victorina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Tu as fait du bon travail. Ils s'assoient sur un coussin. Le coussin est mou, un peu froid. Papa ouvre l'album. Les pages sentent le papier neuf. Ça sent le livre. Oui. Tout calme. Victorina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Victorina. Une page montre une vague. La vague est bleue, tout ronde. Tu vois la vague ? Oui. Elle est bleue. Ils regardent encore un peu. Parce qu'elle reste près, c'est facile. Rester avec l'accompagnant, c'est rester près. On emprunte l'album ? Oui, papa. Papa prend l'album sous le bras. Victorina reste à côté. Tu tiens encore ma main ? Oui. Bravo. Ils marchent vers la porte. Le tapis est encore tout silencieux. Le signet rouge reste dans le gros livre. Le rayon de soleil a bougé un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime rester avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près.
-papa|Tu restes avec moi.
-narrateur|Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un signet dépasse d'un gros livre.
+narrateur|Il est rouge, tout mince.
+narrateur|Le tapis cache les pas.
+narrateur|On n'entend presque plus les chaussures.
+narrateur|Un rayon de soleil glisse entre les rayons.
+narrateur|La poussière y danse, tout doux.
+narrateur|Ça sent le papier et le bois.
+narrateur|Victorina vit ici, avec papa.
+enfant-f|Papa, le signet dépasse !
+papa|Oui.
+papa|Il garde la page.
+papa|Tu vois le rayon de soleil ?
+enfant-f|Oui.
+enfant-f|Il est tout jaune.
+narrateur|En ce moment, ils marchent entre les livres.
+narrateur|Papa tient la main de Victorina.
+narrateur|La main est chaude.
+narrateur|Les pieds de Victorina restent près.
+narrateur|Papa est l'accompagnant.
+narrateur|Victorina aime rester avec l'accompagnant.
+papa|Tu restes avec moi ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu restes avec l'adulte connu.
+narrateur|Ils voient des livres colorés.
+narrateur|Un album a une couverture bleue.
+narrateur|Un bateau blanc est dessus.
+enfant-f|Le bateau !
+papa|On le regarde ensemble.
+narrateur|Papa prend l'album.
+narrateur|Victorina reste à côté.
+narrateur|Ses pieds restent près des pieds de papa.
+papa|Tu restes bien près.
+papa|Tu as fait du bon travail.
+narrateur|Ils s'assoient sur un coussin.
+narrateur|Le coussin est mou, un peu froid.
+narrateur|Papa ouvre l'album.
+narrateur|Les pages sentent le papier neuf.
+enfant-f|Ça sent le livre.
+papa|Oui.
+papa|Tout calme.
+narrateur|Victorina reste avec papa.
+narrateur|L'adulte connu reste près.
+enfant-f|Je reste avec l'accompagnant.
+papa|Oui.
+papa|Bravo, Victorina.
+narrateur|Une page montre une vague.
+narrateur|La vague est bleue, tout ronde.
+papa|Tu vois la vague ?
+enfant-f|Oui.
+enfant-f|Elle est bleue.
+narrateur|Ils regardent encore un peu.
+narrateur|Parce qu'elle reste près, c'est facile.
+narrateur|Rester avec l'accompagnant, c'est rester près.
+papa|On emprunte l'album ?
+enfant-f|Oui, papa.
+narrateur|Papa prend l'album sous le bras.
+narrateur|Victorina reste à côté.
+papa|Tu tiens encore ma main ?
+enfant-f|Oui.
+papa|Bravo.
+narrateur|Ils marchent vers la porte.
+narrateur|Le tapis est encore tout silencieux.
+narrateur|Le signet rouge reste dans le gros livre.
+narrateur|Le rayon de soleil a bougé un peu.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>livres</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Domitille est à la bibliothèque. Que fait-elle ?</t>
+          <t>Victorina est à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1580,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Domitille est à la bibliothèque. Que fait-elle ?</t>
+          <t>narrateur|Victorina est à la bibliothèque.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Domitille reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>Victorina reste avec papa. Papa est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Victorina. Tu restes avec l'adulte connu. L'album bleu pèse un peu. Le bateau blanc reste sur la couverture.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1757,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Domitille reste avec papa. L'accompagnant est là. La main est tenue.</t>
+          <t>narrateur|Victorina reste avec papa.
+narrateur|Papa est l'accompagnant.
+papa|Tu restes avec l'accompagnant ?
+enfant-f|Oui.
+enfant-f|Avec toi.
+papa|Bravo, Victorina.
+papa|Tu restes avec l'adulte connu.
+narrateur|L'album bleu pèse un peu.
+narrateur|Le bateau blanc reste sur la couverture.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Domitille et papa rentrent avec l'album. Ils marchent ensemble.</t>
+          <t>Dehors, l'air est plus vif. Tu as marché près de moi ? Oui, papa. Bravo. Tu as fait du bon travail. Ils rentrent avec l'album. Ils marchent ensemble. Tu restes avec moi, à la bibliothèque. Oui. Le tapis de la maison est plus chaud. L'album attend sur les genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1933,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Domitille et papa rentrent avec l'album. Ils marchent ensemble.</t>
+          <t>narrateur|Dehors, l'air est plus vif.
+papa|Tu as marché près de moi ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Ils rentrent avec l'album.
+narrateur|Ils marchent ensemble.
+papa|Tu restes avec moi, à la bibliothèque.
+enfant-f|Oui.
+narrateur|Le tapis de la maison est plus chaud.
+narrateur|L'album attend sur les genoux.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. C'est du bon travail. Le signet garde encore sa page. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis restée avec papa.
+papa|Avec l'accompagnant.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Le signet garde encore sa page.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un signet dépasse d'un gros livre. Il est rouge, tout mince. Le tapis cache les pas. On n'entend presque plus les chaussures. Un rayon de soleil glisse entre les rayons. La poussière y danse, tout doux. Ça sent le papier et le bois. Victorina vit ici, avec papa. Papa, le signet dépasse ! Oui. Il garde la page. Tu vois le rayon de soleil ? Oui. Il est tout jaune. En ce moment, ils marchent entre les livres. Papa tient la main de Victorina. La main est chaude. Les pieds de Victorina restent près. Papa est l'accompagnant. Victorina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils voient des livres colorés. Un album a une couverture bleue. Un bateau blanc est dessus. Le bateau ! On le regarde ensemble. Papa prend l'album. Victorina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Tu as fait du bon travail. Ils s'assoient sur un coussin. Le coussin est mou, un peu froid. Papa ouvre l'album. Les pages sentent le papier neuf. Ça sent le livre. Oui. Tout calme. Victorina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Victorina. Une page montre une vague. La vague est bleue, tout ronde. Tu vois la vague ? Oui. Elle est bleue. Ils regardent encore un peu. Parce qu'elle reste près, c'est facile. Rester avec l'accompagnant, c'est rester près. On emprunte l'album ? Oui, papa. Papa prend l'album sous le bras. Victorina reste à côté. Tu tiens encore ma main ? Oui. Bravo. Ils marchent vers la porte. Le tapis est encore tout silencieux. Le signet rouge reste dans le gros livre. Le rayon de soleil a bougé un peu.</t>
+          <t>Un signet dépasse d'un gros livre. Il est rouge, tout mince. Le tapis cache les pas. On n'entend presque plus les chaussures. Un rayon de soleil glisse entre les rayons. La poussière y danse, tout doux. Ça sent le papier et le bois. Victorina vit ici, avec papa. Papa, le signet dépasse ! Oui. Il garde la page. Tu vois le rayon de soleil ? Oui. Il est tout jaune. En ce moment, ils marchent entre les livres. Papa tient la main de Victorina. La main est chaude. Les pieds de Victorina restent près. Papa est l'accompagnant. Victorina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils voient des livres colorés. Un album a une couverture bleue. Un bateau blanc est dessus. Le bateau ! On le regarde ensemble. Papa prend l'album. Victorina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Ils s'assoient sur un coussin. Le coussin est mou, un peu froid. Papa ouvre l'album. Les pages sentent le papier neuf. Ça sent le livre. Oui. Tout calme. Victorina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Victorina. Une page montre une vague. La vague est bleue, tout ronde. Tu vois la vague ? Oui. Elle est bleue. Ils regardent encore un peu. Parce qu'elle reste près, c'est facile. Rester avec l'accompagnant, c'est rester près. On emprunte l'album ? Oui, papa. Papa prend l'album sous le bras. Victorina reste à côté. Tu tiens encore ma main ? Oui. Bravo. Ils marchent vers la porte. Le tapis est encore tout silencieux. Le signet rouge reste dans le gros livre. Le rayon de soleil a bougé un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Domitille va à la bibliothèque. Papa vient avec elle. Papa est l'accompagnant. Domitille aime &lt;emphasis level="moderate"&gt;rester&lt;/emphasis&gt; avec l'accompagnant. Elle marche à côté de papa. Papa tient la main. Ses pieds restent près des pieds de papa. Ils voient des livres colorés. Domitille reste près. Papa dit : tu restes avec moi. Domitille hoche la tête. Elle sent la main de papa. La main est chaude. Ils écoutent la dame des livres. Domitille reste avec papa. L'adulte connu est là. Domitille est calme. Elle sourit. Papa prend un album. Domitille reste à côté. Rester avec l'accompagnant, c'est rester près de papa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un signet dépasse d'un gros livre. Il est rouge, tout mince. Le tapis cache les pas. On n'entend presque plus les chaussures. Un rayon de soleil glisse entre les rayons. La poussière y danse, tout doux. Ça sent le papier et le bois. Victorina vit ici, avec papa. Papa, le signet dépasse ! Oui. Il garde la page. Tu vois le rayon de soleil ? Oui. Il est tout jaune. En ce moment, ils marchent entre les livres. Papa tient la main de Victorina. La main est chaude. Les pieds de Victorina restent près. Papa est l'accompagnant. Victorina aime rester avec l'accompagnant. Tu restes avec moi ? Oui, papa. Bravo. Tu restes avec l'adulte connu. Ils voient des livres colorés. Un album a une couverture bleue. Un bateau blanc est dessus. Le bateau ! On le regarde ensemble. Papa prend l'album. Victorina reste à côté. Ses pieds restent près des pieds de papa. Tu restes bien près. Ils s'assoient sur un coussin. Le coussin est mou, un peu froid. Papa ouvre l'album. Les pages sentent le papier neuf. Ça sent le livre. Oui. Tout calme. Victorina reste avec papa. L'adulte connu reste près. Je reste avec l'accompagnant. Oui. Bravo, Victorina. Une page montre une vague. La vague est bleue, tout ronde. Tu vois la vague ? Oui. Elle est bleue. Ils regardent encore un peu. Parce qu'elle reste près, c'est facile. Rester avec l'accompagnant, c'est rester près. On emprunte l'album ? Oui, papa. Papa prend l'album sous le bras. Victorina reste à côté. Tu tiens encore ma main ? Oui. Bravo. Ils marchent vers la porte. Le tapis est encore tout silencieux. Le signet rouge reste dans le gros livre. Le rayon de soleil a bougé un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Victorina reste à côté.
 narrateur|Ses pieds restent près des pieds de papa.
 papa|Tu restes bien près.
-papa|Tu as fait du bon travail.
 narrateur|Ils s'assoient sur un coussin.
 narrateur|Le coussin est mou, un peu froid.
 narrateur|Papa ouvre l'album.
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Domitille est à la bibliothèque. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est à la bibliothèque. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1583,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,7 +1612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Domitille reste avec papa. L'accompagnant est là. La &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est tenue.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina reste avec papa. Papa est l'accompagnant. Tu restes avec l'accompagnant ? Oui. Avec toi. Bravo, Victorina. Tu restes avec l'adulte connu. L'album bleu pèse un peu. Le bateau blanc reste sur la couverture.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1768,7 +1766,6 @@
 narrateur|Le bateau blanc reste sur la couverture.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,12 +1790,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dehors, l'air est plus vif. Tu as marché près de moi ? Oui, papa. Bravo. Tu as fait du bon travail. Ils rentrent avec l'album. Ils marchent ensemble. Tu restes avec moi, à la bibliothèque. Oui. Le tapis de la maison est plus chaud. L'album attend sur les genoux.</t>
+          <t>Dehors, l'air est plus vif. Tu as marché près de moi ? Oui, papa. Bravo. Ils rentrent avec l'album. Ils marchent ensemble. Tu restes avec moi, à la bibliothèque. Oui. Le tapis de la maison est plus chaud. L'album attend sur les genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Domitille et papa rentrent avec l'album. Ils marchent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Dehors, l'air est plus vif. Tu as marché près de moi ? Oui, papa. Bravo. Ils rentrent avec l'album. Ils marchent ensemble. Tu restes avec moi, à la bibliothèque. Oui. Le tapis de la maison est plus chaud. L'album attend sur les genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1934,6 @@
 papa|Tu as marché près de moi ?
 enfant-f|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Ils rentrent avec l'album.
 narrateur|Ils marchent ensemble.
 papa|Tu restes avec moi, à la bibliothèque.
@@ -1946,7 +1942,6 @@
 narrateur|L'album attend sur les genoux.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. C'est du bon travail. Le signet garde encore sa page. L'histoire est finie.</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. Le signet garde encore sa page.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis restée avec papa. Avec l'accompagnant. Bravo. Le signet garde encore sa page.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2109,9 @@
           <t>enfant-f|Je suis restée avec papa.
 papa|Avec l'accompagnant.
 papa|Bravo.
-papa|C'est du bon travail.
-narrateur|Le signet garde encore sa page.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le signet garde encore sa page.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bibliothèque</t>
+          <t>bibliothèque, tapis, albums colorés</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Domitille, papa</t>
+          <t>Victorina, papa</t>
         </is>
       </c>
     </row>
